--- a/Data/Stage/Stage.xlsx
+++ b/Data/Stage/Stage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\DXLibProject_Sample\DXLibProject_Sample\Data\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5C8C84-98D4-4354-B4CD-E8BA0FA363B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE7C31A-3171-40DB-AEE8-1CB5F5BFE524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -420,7 +420,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -438,7 +438,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -476,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -494,7 +494,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -532,7 +532,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>0</v>

--- a/Data/Stage/Stage.xlsx
+++ b/Data/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE7C31A-3171-40DB-AEE8-1CB5F5BFE524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57AFAC3-15CC-457C-887A-7E9EF3F9FFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="3405" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
